--- a/output/yearly_benthic_cover_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_2_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.46835763890088</v>
+        <v>45.31573171219103</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0150243995541</v>
+        <v>99.58661713952679</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95841435469762</v>
+        <v>87.99979502043162</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86546370268838</v>
+        <v>45.90248213612317</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22860173975759</v>
+        <v>2.228679893334418</v>
       </c>
       <c r="E3" t="n">
-        <v>5.666594380613628</v>
+        <v>5.689928174798426</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428672465858632</v>
+        <v>0.7428932977781395</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95187505079288</v>
+        <v>33.96430654697236</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17189334294971</v>
+        <v>34.17309169779441</v>
       </c>
       <c r="I3" t="n">
-        <v>6.553662302836319</v>
+        <v>6.557812298640502</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642920291161645</v>
+        <v>4.643083111113372</v>
       </c>
       <c r="K3" t="n">
-        <v>12.04158564530237</v>
+        <v>12.00020497956837</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85769417936379</v>
+        <v>48.86191569449205</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7647435273545</v>
+        <v>106.7646028101836</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0233621756781</v>
+        <v>87.03283026054068</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56511711412437</v>
+        <v>42.56965041669245</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183372178887974</v>
+        <v>2.181792155021753</v>
       </c>
       <c r="E4" t="n">
-        <v>6.463729622447547</v>
+        <v>6.482939098053438</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444245253911652</v>
+        <v>0.7444514495369196</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26282039744129</v>
+        <v>33.24975372038273</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2435281679936</v>
+        <v>34.24476667869829</v>
       </c>
       <c r="I4" t="n">
-        <v>5.472833999821752</v>
+        <v>5.476305599241802</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652653283694782</v>
+        <v>4.652821559605747</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9766378243219</v>
+        <v>12.96716973945932</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27619888647495</v>
+        <v>44.2810183911082</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81795382492122</v>
+        <v>99.81783854725997</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.76327326367696</v>
+        <v>85.80736492512798</v>
       </c>
       <c r="C5" t="n">
-        <v>42.15437364547542</v>
+        <v>42.19406908747685</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121486124808944</v>
+        <v>2.121763967845743</v>
       </c>
       <c r="E5" t="n">
-        <v>7.041985632814412</v>
+        <v>7.06652117664233</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457464284536991</v>
+        <v>0.745773559540544</v>
       </c>
       <c r="G5" t="n">
-        <v>32.32001059073873</v>
+        <v>32.33494502273046</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30433570887016</v>
+        <v>34.30558373886502</v>
       </c>
       <c r="I5" t="n">
-        <v>4.568793600155391</v>
+        <v>4.571692712375495</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660915177835619</v>
+        <v>4.6610847471284</v>
       </c>
       <c r="K5" t="n">
-        <v>14.23672673632303</v>
+        <v>14.19263507487201</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45687645153985</v>
+        <v>43.46117623767221</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84797683333831</v>
+        <v>99.84788040002107</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.28579872595597</v>
+        <v>84.43888804730688</v>
       </c>
       <c r="C6" t="n">
-        <v>41.38630890578305</v>
+        <v>41.53548417010121</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049012576947859</v>
+        <v>2.05492770708607</v>
       </c>
       <c r="E6" t="n">
-        <v>7.436931084250983</v>
+        <v>7.47983714286207</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468710081356632</v>
+        <v>0.7468968515094151</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2159044610653</v>
+        <v>31.31638365118302</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35606637424051</v>
+        <v>34.35725516943308</v>
       </c>
       <c r="I6" t="n">
-        <v>3.813069420467766</v>
+        <v>3.815482203299362</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667943800847895</v>
+        <v>4.668105321933844</v>
       </c>
       <c r="K6" t="n">
-        <v>15.71420127404402</v>
+        <v>15.56111195269313</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77257888683528</v>
+        <v>42.776412412973</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87308906666235</v>
+        <v>99.87300853576734</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.6177537044847</v>
+        <v>82.88629020492498</v>
       </c>
       <c r="C7" t="n">
-        <v>40.3102670839935</v>
+        <v>40.57537559405026</v>
       </c>
       <c r="D7" t="n">
-        <v>1.967562326439644</v>
+        <v>1.979358647325999</v>
       </c>
       <c r="E7" t="n">
-        <v>7.671578614235426</v>
+        <v>7.73537599563528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478297497238573</v>
+        <v>0.7478531215286653</v>
       </c>
       <c r="G7" t="n">
-        <v>29.97504178076806</v>
+        <v>30.16473745971607</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40016848729744</v>
+        <v>34.40124359031859</v>
       </c>
       <c r="I7" t="n">
-        <v>3.181636810246161</v>
+        <v>3.183639380846206</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673935935774108</v>
+        <v>4.674082009554158</v>
       </c>
       <c r="K7" t="n">
-        <v>17.38224629551528</v>
+        <v>17.11370979507502</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20156802547821</v>
+        <v>42.20492899411639</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89408140498701</v>
+        <v>99.89401438324168</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.40939425221896</v>
+        <v>87.67423505656581</v>
       </c>
       <c r="C8" t="n">
-        <v>42.54356985076296</v>
+        <v>42.79504213962124</v>
       </c>
       <c r="D8" t="n">
-        <v>1.971776821108179</v>
+        <v>1.983594459387781</v>
       </c>
       <c r="E8" t="n">
-        <v>9.457547648123022</v>
+        <v>9.512870479984507</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494315919886895</v>
+        <v>0.7494535213737831</v>
       </c>
       <c r="G8" t="n">
-        <v>30.45594160079818</v>
+        <v>30.6407047351554</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47385323147972</v>
+        <v>34.47486198319401</v>
       </c>
       <c r="I8" t="n">
-        <v>5.616895908791864</v>
+        <v>5.628665368884199</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683947449929309</v>
+        <v>4.684084508586144</v>
       </c>
       <c r="K8" t="n">
-        <v>12.59060574778105</v>
+        <v>12.32576494343418</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6789947247339</v>
+        <v>44.69197139058742</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81317032327792</v>
+        <v>99.81277847364284</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.27476530773217</v>
+        <v>85.68350196393391</v>
       </c>
       <c r="C9" t="n">
-        <v>41.28019314930793</v>
+        <v>41.67764918228122</v>
       </c>
       <c r="D9" t="n">
-        <v>1.874717860162826</v>
+        <v>1.893336187814073</v>
       </c>
       <c r="E9" t="n">
-        <v>9.773562694036796</v>
+        <v>9.863200428910519</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508053197763924</v>
+        <v>0.7508235941369151</v>
       </c>
       <c r="G9" t="n">
-        <v>28.9567749533657</v>
+        <v>29.24647970286274</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53704470971406</v>
+        <v>34.53788533029808</v>
       </c>
       <c r="I9" t="n">
-        <v>4.689326522073936</v>
+        <v>4.69912925655585</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692533248602452</v>
+        <v>4.692647463355719</v>
       </c>
       <c r="K9" t="n">
-        <v>14.72523469226784</v>
+        <v>14.31649803606611</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83854727206892</v>
+        <v>43.84950096585032</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84397511364469</v>
+        <v>99.84364818419765</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.05071597741259</v>
+        <v>83.5229616146987</v>
       </c>
       <c r="C10" t="n">
-        <v>39.78310684731021</v>
+        <v>40.24595640567737</v>
       </c>
       <c r="D10" t="n">
-        <v>1.774818138486399</v>
+        <v>1.796379500839526</v>
       </c>
       <c r="E10" t="n">
-        <v>9.905068820307482</v>
+        <v>10.01178987579694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519847537351035</v>
+        <v>0.7519988330735687</v>
       </c>
       <c r="G10" t="n">
-        <v>27.41373009314503</v>
+        <v>27.74878383885891</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59129867181477</v>
+        <v>34.59194632138414</v>
       </c>
       <c r="I10" t="n">
-        <v>3.913910789079423</v>
+        <v>3.922070538035815</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699904710844396</v>
+        <v>4.699992706709804</v>
       </c>
       <c r="K10" t="n">
-        <v>16.94928402258739</v>
+        <v>16.4770383853013</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13735006004479</v>
+        <v>43.14647384078368</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8697409299424</v>
+        <v>99.86946863176235</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.686446815735</v>
+        <v>81.29775090889453</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02493136470187</v>
+        <v>38.6284733619364</v>
       </c>
       <c r="D11" t="n">
-        <v>1.669732113915904</v>
+        <v>1.697602097198561</v>
       </c>
       <c r="E11" t="n">
-        <v>9.862927211593369</v>
+        <v>10.00673522158884</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529993714588259</v>
+        <v>0.7530079324075278</v>
       </c>
       <c r="G11" t="n">
-        <v>25.7905779224139</v>
+        <v>26.22296325333347</v>
       </c>
       <c r="H11" t="n">
-        <v>34.637971087106</v>
+        <v>34.63836489074626</v>
       </c>
       <c r="I11" t="n">
-        <v>3.265993037629349</v>
+        <v>3.27277793607283</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70624607161766</v>
+        <v>4.706299577547048</v>
       </c>
       <c r="K11" t="n">
-        <v>19.31355318426501</v>
+        <v>18.70224909110548</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55279570689201</v>
+        <v>42.56033114312379</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89128025585889</v>
+        <v>99.89105359616568</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.29255721241506</v>
+        <v>78.98994993460265</v>
       </c>
       <c r="C12" t="n">
-        <v>36.13595716017726</v>
+        <v>36.82706002135777</v>
       </c>
       <c r="D12" t="n">
-        <v>1.564449333864061</v>
+        <v>1.596143399356249</v>
       </c>
       <c r="E12" t="n">
-        <v>9.695169581493799</v>
+        <v>9.863750042932063</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538729267982988</v>
+        <v>0.7538755770175379</v>
       </c>
       <c r="G12" t="n">
-        <v>24.16438667880933</v>
+        <v>24.65572455255635</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67815463272175</v>
+        <v>34.67827654280673</v>
       </c>
       <c r="I12" t="n">
-        <v>2.724818266238458</v>
+        <v>2.73045746357411</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711705792489366</v>
+        <v>4.711722356359611</v>
       </c>
       <c r="K12" t="n">
-        <v>21.70744278758494</v>
+        <v>21.01005006539734</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06587802341478</v>
+        <v>42.07197941502067</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90927797117698</v>
+        <v>99.90908950177578</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.86646446178291</v>
+        <v>76.74360897488715</v>
       </c>
       <c r="C13" t="n">
-        <v>34.13023275175534</v>
+        <v>35.00238281542086</v>
       </c>
       <c r="D13" t="n">
-        <v>1.458759855375085</v>
+        <v>1.498346333040784</v>
       </c>
       <c r="E13" t="n">
-        <v>9.419018088178399</v>
+        <v>9.638995040794187</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546257913343219</v>
+        <v>0.7546213725836904</v>
       </c>
       <c r="G13" t="n">
-        <v>22.53191359655147</v>
+        <v>23.14504729755864</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71278640137881</v>
+        <v>34.71258313884974</v>
       </c>
       <c r="I13" t="n">
-        <v>2.272949533125317</v>
+        <v>2.277632213412036</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716411195839511</v>
+        <v>4.716383578648064</v>
       </c>
       <c r="K13" t="n">
-        <v>24.13353553821709</v>
+        <v>23.25639102511286</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66054231374316</v>
+        <v>41.66538011881143</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9243106037156</v>
+        <v>99.92415395934515</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.93475089597572</v>
+        <v>83.5532224972201</v>
       </c>
       <c r="C14" t="n">
-        <v>38.53216706774464</v>
+        <v>39.20752833910624</v>
       </c>
       <c r="D14" t="n">
-        <v>1.460483451806669</v>
+        <v>1.500130077170389</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86163110944383</v>
+        <v>11.98688171729006</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555174187782309</v>
+        <v>0.7555197306026198</v>
       </c>
       <c r="G14" t="n">
-        <v>24.50006273602241</v>
+        <v>25.01167240363751</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69532784046139</v>
+        <v>36.59297910931149</v>
       </c>
       <c r="I14" t="n">
-        <v>2.93974447209925</v>
+        <v>2.984041142941662</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721983867363941</v>
+        <v>4.721998316266372</v>
       </c>
       <c r="K14" t="n">
-        <v>17.06524910402427</v>
+        <v>16.4467775027799</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30470799093776</v>
+        <v>44.24634439344539</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90212416270668</v>
+        <v>99.90065023533154</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.08732591262397</v>
+        <v>82.89422435074445</v>
       </c>
       <c r="C15" t="n">
-        <v>38.1385675760465</v>
+        <v>39.0096559409668</v>
       </c>
       <c r="D15" t="n">
-        <v>1.429182317338655</v>
+        <v>1.475927573524495</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01611661801394</v>
+        <v>12.20835512496235</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562697476024478</v>
+        <v>0.7562759683202122</v>
       </c>
       <c r="G15" t="n">
-        <v>23.9749765002103</v>
+        <v>24.60814400183333</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73186829891053</v>
+        <v>36.62960686353237</v>
       </c>
       <c r="I15" t="n">
-        <v>2.452226508032795</v>
+        <v>2.489190016570355</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726685922515297</v>
+        <v>4.726724802001325</v>
       </c>
       <c r="K15" t="n">
-        <v>17.91267408737603</v>
+        <v>17.10577564925557</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86709876790803</v>
+        <v>43.80167837802925</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91834043133056</v>
+        <v>99.91710996825162</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.46511706448892</v>
+        <v>80.57762374546432</v>
       </c>
       <c r="C16" t="n">
-        <v>35.89492335003483</v>
+        <v>37.07782289899509</v>
       </c>
       <c r="D16" t="n">
-        <v>1.330173236835485</v>
+        <v>1.387828375172057</v>
       </c>
       <c r="E16" t="n">
-        <v>11.52455854258941</v>
+        <v>11.8256472175109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569185772987145</v>
+        <v>0.7569254908577323</v>
       </c>
       <c r="G16" t="n">
-        <v>22.31406847638926</v>
+        <v>23.13926585469919</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76338182570073</v>
+        <v>36.66106595544456</v>
       </c>
       <c r="I16" t="n">
-        <v>2.045275297558359</v>
+        <v>2.076106533919077</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730741108116963</v>
+        <v>4.730784317860826</v>
       </c>
       <c r="K16" t="n">
-        <v>20.53488293551109</v>
+        <v>19.42237625453565</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50207631145315</v>
+        <v>43.43065667934232</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93188259699907</v>
+        <v>99.93085583287306</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.13786789036983</v>
+        <v>82.35429256583981</v>
       </c>
       <c r="C17" t="n">
-        <v>37.116445486704</v>
+        <v>38.37475749515219</v>
       </c>
       <c r="D17" t="n">
-        <v>1.331285469147625</v>
+        <v>1.388985404414633</v>
       </c>
       <c r="E17" t="n">
-        <v>12.29966579906078</v>
+        <v>12.64022531027078</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575514792967533</v>
+        <v>0.7575565378539179</v>
       </c>
       <c r="G17" t="n">
-        <v>22.75897787720862</v>
+        <v>23.61998318741278</v>
       </c>
       <c r="H17" t="n">
-        <v>37.2203731063462</v>
+        <v>37.15305638100501</v>
       </c>
       <c r="I17" t="n">
-        <v>2.035317413705148</v>
+        <v>2.059757383295723</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734696745604706</v>
+        <v>4.734728361586985</v>
       </c>
       <c r="K17" t="n">
-        <v>18.86213210963016</v>
+        <v>17.64570743416019</v>
       </c>
       <c r="L17" t="n">
-        <v>43.95363517057628</v>
+        <v>43.91093368405861</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93221276691045</v>
+        <v>99.93139861337099</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.60550859212745</v>
+        <v>80.19099186457788</v>
       </c>
       <c r="C18" t="n">
-        <v>34.8978043005971</v>
+        <v>36.52952715303681</v>
       </c>
       <c r="D18" t="n">
-        <v>1.239533421806546</v>
+        <v>1.310109864479062</v>
       </c>
       <c r="E18" t="n">
-        <v>11.73486063078801</v>
+        <v>12.20871355477958</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580967363504759</v>
+        <v>0.7580974329055581</v>
       </c>
       <c r="G18" t="n">
-        <v>21.19043163824064</v>
+        <v>22.27868836800361</v>
       </c>
       <c r="H18" t="n">
-        <v>37.24716293058002</v>
+        <v>37.17958364774437</v>
       </c>
       <c r="I18" t="n">
-        <v>1.697318632171291</v>
+        <v>1.717690041005963</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738104602190473</v>
+        <v>4.738108955659737</v>
       </c>
       <c r="K18" t="n">
-        <v>21.39449140787255</v>
+        <v>19.80900813542213</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6511676967052</v>
+        <v>43.60424922867176</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94346340517485</v>
+        <v>99.94278451713069</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.55857284031865</v>
+        <v>79.36790440681438</v>
       </c>
       <c r="C19" t="n">
-        <v>34.10634021542406</v>
+        <v>35.97108982365515</v>
       </c>
       <c r="D19" t="n">
-        <v>1.202056093639883</v>
+        <v>1.280756634114011</v>
       </c>
       <c r="E19" t="n">
-        <v>11.61680851098062</v>
+        <v>12.17388685565344</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758559562580715</v>
+        <v>0.7585534525721671</v>
       </c>
       <c r="G19" t="n">
-        <v>20.54973833660934</v>
+        <v>21.77953063350535</v>
       </c>
       <c r="H19" t="n">
-        <v>37.26990272509391</v>
+        <v>37.20194834732489</v>
       </c>
       <c r="I19" t="n">
-        <v>1.420510345284705</v>
+        <v>1.432269405068477</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740997266129468</v>
+        <v>4.740959078576043</v>
       </c>
       <c r="K19" t="n">
-        <v>22.44142715968135</v>
+        <v>20.63209559318561</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40491117030994</v>
+        <v>43.34910097090908</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95267854541535</v>
+        <v>99.95228638774984</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.83789469744764</v>
+        <v>76.96863082735969</v>
       </c>
       <c r="C20" t="n">
-        <v>31.60377746445131</v>
+        <v>33.79238030264978</v>
       </c>
       <c r="D20" t="n">
-        <v>1.104629984287428</v>
+        <v>1.194160684899226</v>
       </c>
       <c r="E20" t="n">
-        <v>10.87266855322833</v>
+        <v>11.54980159412493</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589597275524707</v>
+        <v>0.7589457533672985</v>
       </c>
       <c r="G20" t="n">
-        <v>18.88419122533898</v>
+        <v>20.30694866248509</v>
       </c>
       <c r="H20" t="n">
-        <v>37.28956381738913</v>
+        <v>37.22118806453613</v>
       </c>
       <c r="I20" t="n">
-        <v>1.184383092448359</v>
+        <v>1.194175109401417</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743498297202941</v>
+        <v>4.743410958545614</v>
       </c>
       <c r="K20" t="n">
-        <v>25.16210530255237</v>
+        <v>23.0313691726403</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19465861229396</v>
+        <v>43.136465263458</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96054137929764</v>
+        <v>99.96021473874808</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.98604060790807</v>
+        <v>82.64694173899872</v>
       </c>
       <c r="C21" t="n">
-        <v>35.448707946753</v>
+        <v>37.28969153652316</v>
       </c>
       <c r="D21" t="n">
-        <v>1.105391531492627</v>
+        <v>1.194999176770138</v>
       </c>
       <c r="E21" t="n">
-        <v>12.93519542102562</v>
+        <v>13.44412896639136</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594829648967375</v>
+        <v>0.7594786547202814</v>
       </c>
       <c r="G21" t="n">
-        <v>20.67307685939763</v>
+        <v>21.91726806858818</v>
       </c>
       <c r="H21" t="n">
-        <v>39.09113837014227</v>
+        <v>38.84338397304014</v>
       </c>
       <c r="I21" t="n">
-        <v>1.674986930348567</v>
+        <v>1.74094130748687</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746768530604609</v>
+        <v>4.746741592001758</v>
       </c>
       <c r="K21" t="n">
-        <v>19.01395939209193</v>
+        <v>17.35305826100126</v>
       </c>
       <c r="L21" t="n">
-        <v>45.48153822893086</v>
+        <v>45.29925954428013</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9442055677758</v>
+        <v>99.94200934180456</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_2_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.31573171219103</v>
+        <v>44.95167949068463</v>
       </c>
       <c r="M2" t="n">
-        <v>99.58661713952679</v>
+        <v>100.7573780521266</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99979502043162</v>
+        <v>88.0578555796608</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90248213612317</v>
+        <v>45.91985388904213</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228679893334418</v>
+        <v>2.228815645516693</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689928174798426</v>
+        <v>5.703061415287742</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428932977781395</v>
+        <v>0.7429385485055644</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96430654697236</v>
+        <v>33.96972138558069</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17309169779441</v>
+        <v>34.17517323125596</v>
       </c>
       <c r="I3" t="n">
-        <v>6.557812298640502</v>
+        <v>6.59477942535436</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643083111113372</v>
+        <v>4.643365928159778</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00020497956837</v>
+        <v>11.94214442033921</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86191569449205</v>
+        <v>48.90129195866322</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646028101836</v>
+        <v>106.7632902680446</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03283026054068</v>
+        <v>87.27307911927484</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56965041669245</v>
+        <v>42.77570212135953</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181792155021753</v>
+        <v>2.191672455426708</v>
       </c>
       <c r="E4" t="n">
-        <v>6.482939098053438</v>
+        <v>6.525888169318256</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444514495369196</v>
+        <v>0.7445012748031586</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24975372038273</v>
+        <v>33.40361632378857</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24476667869829</v>
+        <v>34.2470586409453</v>
       </c>
       <c r="I4" t="n">
-        <v>5.476305599241802</v>
+        <v>5.50720928747311</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652821559605747</v>
+        <v>4.653132967519742</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96716973945932</v>
+        <v>12.72692088072515</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2810183911082</v>
+        <v>44.31418868054438</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81783854725997</v>
+        <v>99.81681168262907</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.80736492512798</v>
+        <v>86.23210288408606</v>
       </c>
       <c r="C5" t="n">
-        <v>42.19406908747685</v>
+        <v>42.58959216696357</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121763967845743</v>
+        <v>2.141306536778889</v>
       </c>
       <c r="E5" t="n">
-        <v>7.06652117664233</v>
+        <v>7.142168956920791</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745773559540544</v>
+        <v>0.7458243870309287</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33494502273046</v>
+        <v>32.63598162630394</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30558373886502</v>
+        <v>34.30792180342272</v>
       </c>
       <c r="I5" t="n">
-        <v>4.571692712375495</v>
+        <v>4.597497154685467</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6610847471284</v>
+        <v>4.661402418943305</v>
       </c>
       <c r="K5" t="n">
-        <v>14.19263507487201</v>
+        <v>13.76789711591398</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46117623767221</v>
+        <v>43.48953268135929</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84788040002107</v>
+        <v>99.84702196423684</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.43888804730688</v>
+        <v>84.95649974742032</v>
       </c>
       <c r="C6" t="n">
-        <v>41.53548417010121</v>
+        <v>42.02821964185294</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05492770708607</v>
+        <v>2.079272485099831</v>
       </c>
       <c r="E6" t="n">
-        <v>7.47983714286207</v>
+        <v>7.57476156784656</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468968515094151</v>
+        <v>0.7469472125339587</v>
       </c>
       <c r="G6" t="n">
-        <v>31.31638365118302</v>
+        <v>31.69051112218435</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35725516943308</v>
+        <v>34.35957177656211</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815482203299362</v>
+        <v>3.83701550485627</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668105321933844</v>
+        <v>4.668420078337243</v>
       </c>
       <c r="K6" t="n">
-        <v>15.56111195269313</v>
+        <v>15.04350025257969</v>
       </c>
       <c r="L6" t="n">
-        <v>42.776412412973</v>
+        <v>42.80057185127058</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87300853576734</v>
+        <v>99.87229174570321</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.88629020492498</v>
+        <v>83.54295805951396</v>
       </c>
       <c r="C7" t="n">
-        <v>40.57537559405026</v>
+        <v>41.21086951987727</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979358647325999</v>
+        <v>2.01074888786698</v>
       </c>
       <c r="E7" t="n">
-        <v>7.73537599563528</v>
+        <v>7.858730613311114</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478531215286653</v>
+        <v>0.7479013820566779</v>
       </c>
       <c r="G7" t="n">
-        <v>30.16473745971607</v>
+        <v>30.64613245810778</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40124359031859</v>
+        <v>34.40346357460719</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183639380846206</v>
+        <v>3.201597505709993</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674082009554158</v>
+        <v>4.674383637854238</v>
       </c>
       <c r="K7" t="n">
-        <v>17.11370979507502</v>
+        <v>16.45704194048604</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20492899411639</v>
+        <v>42.2255047756129</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89401438324168</v>
+        <v>99.8934162359762</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.67423505656581</v>
+        <v>88.45339156921442</v>
       </c>
       <c r="C8" t="n">
-        <v>42.79504213962124</v>
+        <v>43.53838181592918</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983594459387781</v>
+        <v>2.015038410189309</v>
       </c>
       <c r="E8" t="n">
-        <v>9.512870479984507</v>
+        <v>9.709805332370816</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494535213737831</v>
+        <v>0.749496876995201</v>
       </c>
       <c r="G8" t="n">
-        <v>30.6407047351554</v>
+        <v>31.15692144701301</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47486198319401</v>
+        <v>34.47685634177925</v>
       </c>
       <c r="I8" t="n">
-        <v>5.628665368884199</v>
+        <v>5.660917679646817</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684084508586144</v>
+        <v>4.684355481220007</v>
       </c>
       <c r="K8" t="n">
-        <v>12.32576494343418</v>
+        <v>11.54660843078557</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69197139058742</v>
+        <v>44.72671418745223</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81277847364284</v>
+        <v>99.81170443416698</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.68350196393391</v>
+        <v>86.57600685159532</v>
       </c>
       <c r="C9" t="n">
-        <v>41.67764918228122</v>
+        <v>42.54011591556684</v>
       </c>
       <c r="D9" t="n">
-        <v>1.893336187814073</v>
+        <v>1.930325083050342</v>
       </c>
       <c r="E9" t="n">
-        <v>9.863200428910519</v>
+        <v>10.08926896361152</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508235941369151</v>
+        <v>0.7508606627198033</v>
       </c>
       <c r="G9" t="n">
-        <v>29.24647970286274</v>
+        <v>29.84706726962492</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53788533029808</v>
+        <v>34.53959048511096</v>
       </c>
       <c r="I9" t="n">
-        <v>4.69912925655585</v>
+        <v>4.726015245478997</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692647463355719</v>
+        <v>4.692879141998771</v>
       </c>
       <c r="K9" t="n">
-        <v>14.31649803606611</v>
+        <v>13.42399314840468</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84950096585032</v>
+        <v>43.87864322270494</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84364818419765</v>
+        <v>99.84275228667646</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.5229616146987</v>
+        <v>84.45178740133619</v>
       </c>
       <c r="C10" t="n">
-        <v>40.24595640567737</v>
+        <v>41.149693535064</v>
       </c>
       <c r="D10" t="n">
-        <v>1.796379500839526</v>
+        <v>1.835237597074658</v>
       </c>
       <c r="E10" t="n">
-        <v>10.01178987579694</v>
+        <v>10.24968622518218</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519988330735687</v>
+        <v>0.7520296741280165</v>
       </c>
       <c r="G10" t="n">
-        <v>27.74878383885891</v>
+        <v>28.37680580157678</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59194632138414</v>
+        <v>34.59336500988876</v>
       </c>
       <c r="I10" t="n">
-        <v>3.922070538035815</v>
+        <v>3.944477630185699</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699992706709804</v>
+        <v>4.700185463300103</v>
       </c>
       <c r="K10" t="n">
-        <v>16.4770383853013</v>
+        <v>15.54821259866379</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14647384078368</v>
+        <v>43.1708156650089</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86946863176235</v>
+        <v>99.8687217987367</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.29775090889453</v>
+        <v>82.19731468294445</v>
       </c>
       <c r="C11" t="n">
-        <v>38.6284733619364</v>
+        <v>39.50713069487344</v>
       </c>
       <c r="D11" t="n">
-        <v>1.697602097198561</v>
+        <v>1.735293788753534</v>
       </c>
       <c r="E11" t="n">
-        <v>10.00673522158884</v>
+        <v>10.24008172444141</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530079324075278</v>
+        <v>0.7530334659295552</v>
       </c>
       <c r="G11" t="n">
-        <v>26.22296325333347</v>
+        <v>26.83145491931543</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63836489074626</v>
+        <v>34.63953943275955</v>
       </c>
       <c r="I11" t="n">
-        <v>3.27277793607283</v>
+        <v>3.291452189685252</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706299577547048</v>
+        <v>4.706459162059721</v>
       </c>
       <c r="K11" t="n">
-        <v>18.70224909110548</v>
+        <v>17.80268531705556</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56033114312379</v>
+        <v>42.58061516501028</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89105359616568</v>
+        <v>99.89043117693927</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.98994993460265</v>
+        <v>79.66203762872799</v>
       </c>
       <c r="C12" t="n">
-        <v>36.82706002135777</v>
+        <v>37.48173298167976</v>
       </c>
       <c r="D12" t="n">
-        <v>1.596143399356249</v>
+        <v>1.623789491916224</v>
       </c>
       <c r="E12" t="n">
-        <v>9.863750042932063</v>
+        <v>10.03975901614292</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538755770175379</v>
+        <v>0.7538987259727841</v>
       </c>
       <c r="G12" t="n">
-        <v>24.65572455255635</v>
+        <v>25.10735348283804</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67827654280673</v>
+        <v>34.67934139474807</v>
       </c>
       <c r="I12" t="n">
-        <v>2.73045746357411</v>
+        <v>2.746028479780045</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711722356359611</v>
+        <v>4.711867037329901</v>
       </c>
       <c r="K12" t="n">
-        <v>21.01005006539734</v>
+        <v>20.33796237127201</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07197941502067</v>
+        <v>42.08887541955698</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90908950177578</v>
+        <v>99.90857077250875</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.74360897488715</v>
+        <v>77.18671024649439</v>
       </c>
       <c r="C13" t="n">
-        <v>35.00238281542086</v>
+        <v>35.43086617905027</v>
       </c>
       <c r="D13" t="n">
-        <v>1.498346333040784</v>
+        <v>1.515978088022411</v>
       </c>
       <c r="E13" t="n">
-        <v>9.638995040794187</v>
+        <v>9.754939953798837</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546213725836904</v>
+        <v>0.7546444916837086</v>
       </c>
       <c r="G13" t="n">
-        <v>23.14504729755864</v>
+        <v>23.44035228562704</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71258313884974</v>
+        <v>34.7136466174506</v>
       </c>
       <c r="I13" t="n">
-        <v>2.277632213412036</v>
+        <v>2.290620736888614</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716383578648064</v>
+        <v>4.716528073023179</v>
       </c>
       <c r="K13" t="n">
-        <v>23.25639102511286</v>
+        <v>22.81328975350561</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66538011881143</v>
+        <v>41.67956549856135</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92415395934515</v>
+        <v>99.92372143111723</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.5532224972201</v>
+        <v>83.91299376091838</v>
       </c>
       <c r="C14" t="n">
-        <v>39.20752833910624</v>
+        <v>39.4584459158497</v>
       </c>
       <c r="D14" t="n">
-        <v>1.500130077170389</v>
+        <v>1.517900030556369</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98688171729006</v>
+        <v>12.03206379733752</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555197306026198</v>
+        <v>0.7556012227592058</v>
       </c>
       <c r="G14" t="n">
-        <v>25.01167240363751</v>
+        <v>25.20290590588072</v>
       </c>
       <c r="H14" t="n">
-        <v>36.59297910931149</v>
+        <v>36.49049241253539</v>
       </c>
       <c r="I14" t="n">
-        <v>2.984041142941662</v>
+        <v>3.191522749604146</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721998316266372</v>
+        <v>4.722507642245036</v>
       </c>
       <c r="K14" t="n">
-        <v>16.4467775027799</v>
+        <v>16.08700623908162</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24634439344539</v>
+        <v>44.34829845537618</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90065023533154</v>
+        <v>99.89375061030749</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.89422435074445</v>
+        <v>83.08712795715189</v>
       </c>
       <c r="C15" t="n">
-        <v>39.0096559409668</v>
+        <v>39.12431449496604</v>
       </c>
       <c r="D15" t="n">
-        <v>1.475927573524495</v>
+        <v>1.486955461424852</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20835512496235</v>
+        <v>12.23207280706835</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562759683202122</v>
+        <v>0.7564083053609625</v>
       </c>
       <c r="G15" t="n">
-        <v>24.60814400183333</v>
+        <v>24.69066789257226</v>
       </c>
       <c r="H15" t="n">
-        <v>36.62960686353237</v>
+        <v>36.53102848190528</v>
       </c>
       <c r="I15" t="n">
-        <v>2.489190016570355</v>
+        <v>2.662443100314163</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726724802001325</v>
+        <v>4.727551908506015</v>
       </c>
       <c r="K15" t="n">
-        <v>17.10577564925557</v>
+        <v>16.91287204284812</v>
       </c>
       <c r="L15" t="n">
-        <v>43.80167837802925</v>
+        <v>43.87416005247461</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91710996825162</v>
+        <v>99.91134659028877</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.57762374546432</v>
+        <v>80.52570892686379</v>
       </c>
       <c r="C16" t="n">
-        <v>37.07782289899509</v>
+        <v>36.97446920007085</v>
       </c>
       <c r="D16" t="n">
-        <v>1.387828375172057</v>
+        <v>1.389070943139929</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8256472175109</v>
+        <v>11.79697362471047</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569254908577323</v>
+        <v>0.7571036476068864</v>
       </c>
       <c r="G16" t="n">
-        <v>23.13926585469919</v>
+        <v>23.06531044542885</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66106595544456</v>
+        <v>36.56461030168501</v>
       </c>
       <c r="I16" t="n">
-        <v>2.076106533919077</v>
+        <v>2.220742166749605</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730784317860826</v>
+        <v>4.73189779754304</v>
       </c>
       <c r="K16" t="n">
-        <v>19.42237625453565</v>
+        <v>19.47429107313622</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43065667934232</v>
+        <v>43.47728297400644</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93085583287306</v>
+        <v>99.9260432472135</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.35429256583981</v>
+        <v>82.22114794218984</v>
       </c>
       <c r="C17" t="n">
-        <v>38.37475749515219</v>
+        <v>38.19069579919182</v>
       </c>
       <c r="D17" t="n">
-        <v>1.388985404414633</v>
+        <v>1.390342337124854</v>
       </c>
       <c r="E17" t="n">
-        <v>12.64022531027078</v>
+        <v>12.58757000281672</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575565378539179</v>
+        <v>0.7577966122306776</v>
       </c>
       <c r="G17" t="n">
-        <v>23.61998318741278</v>
+        <v>23.48994216817073</v>
       </c>
       <c r="H17" t="n">
-        <v>37.15305638100501</v>
+        <v>37.0015977134741</v>
       </c>
       <c r="I17" t="n">
-        <v>2.059757383295723</v>
+        <v>2.257670281931023</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734728361586985</v>
+        <v>4.736228826441735</v>
       </c>
       <c r="K17" t="n">
-        <v>17.64570743416019</v>
+        <v>17.77885205781015</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91093368405861</v>
+        <v>43.95526528423954</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93139861337099</v>
+        <v>99.92481314124151</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.19099186457788</v>
+        <v>79.76446175699081</v>
       </c>
       <c r="C18" t="n">
-        <v>36.52952715303681</v>
+        <v>36.0825302520788</v>
       </c>
       <c r="D18" t="n">
-        <v>1.310109864479062</v>
+        <v>1.300202853144793</v>
       </c>
       <c r="E18" t="n">
-        <v>12.20871355477958</v>
+        <v>12.08529737959498</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580974329055581</v>
+        <v>0.7583928820460359</v>
       </c>
       <c r="G18" t="n">
-        <v>22.27868836800361</v>
+        <v>21.96702855961373</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17958364774437</v>
+        <v>37.03071230105669</v>
       </c>
       <c r="I18" t="n">
-        <v>1.717690041005963</v>
+        <v>1.882872268746862</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738108955659737</v>
+        <v>4.739955512787724</v>
       </c>
       <c r="K18" t="n">
-        <v>19.80900813542213</v>
+        <v>20.2355382430092</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60424922867176</v>
+        <v>43.61921844152502</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94278451713069</v>
+        <v>99.93728693661302</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.36790440681438</v>
+        <v>78.72102102700914</v>
       </c>
       <c r="C19" t="n">
-        <v>35.97108982365515</v>
+        <v>35.32899098174381</v>
       </c>
       <c r="D19" t="n">
-        <v>1.280756634114011</v>
+        <v>1.262665878537715</v>
       </c>
       <c r="E19" t="n">
-        <v>12.17388685565344</v>
+        <v>11.99807764455763</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585534525721671</v>
+        <v>0.7588970909701506</v>
       </c>
       <c r="G19" t="n">
-        <v>21.77953063350535</v>
+        <v>21.33283844747793</v>
       </c>
       <c r="H19" t="n">
-        <v>37.20194834732489</v>
+        <v>37.05533175101532</v>
       </c>
       <c r="I19" t="n">
-        <v>1.432269405068477</v>
+        <v>1.570103395886944</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740959078576043</v>
+        <v>4.743106818563441</v>
       </c>
       <c r="K19" t="n">
-        <v>20.63209559318561</v>
+        <v>21.27897897299088</v>
       </c>
       <c r="L19" t="n">
-        <v>43.34910097090908</v>
+        <v>43.33972803780013</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95228638774984</v>
+        <v>99.94769799253481</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.96863082735969</v>
+        <v>76.0620849972582</v>
       </c>
       <c r="C20" t="n">
-        <v>33.79238030264978</v>
+        <v>32.9116129478879</v>
       </c>
       <c r="D20" t="n">
-        <v>1.194160684899226</v>
+        <v>1.166283449631338</v>
       </c>
       <c r="E20" t="n">
-        <v>11.54980159412493</v>
+        <v>11.30042954740128</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589457533672985</v>
+        <v>0.7593324920581895</v>
       </c>
       <c r="G20" t="n">
-        <v>20.30694866248509</v>
+        <v>19.70444979772965</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22118806453613</v>
+        <v>37.07659146060442</v>
       </c>
       <c r="I20" t="n">
-        <v>1.194175109401417</v>
+        <v>1.309170174469625</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743410958545614</v>
+        <v>4.745828075363685</v>
       </c>
       <c r="K20" t="n">
-        <v>23.0313691726403</v>
+        <v>23.93791500274181</v>
       </c>
       <c r="L20" t="n">
-        <v>43.136465263458</v>
+        <v>43.10685806615122</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96021473874808</v>
+        <v>99.95638601678093</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.64694173899872</v>
+        <v>82.08192630025063</v>
       </c>
       <c r="C21" t="n">
-        <v>37.28969153652316</v>
+        <v>36.56486771792108</v>
       </c>
       <c r="D21" t="n">
-        <v>1.194999176770138</v>
+        <v>1.167220211995549</v>
       </c>
       <c r="E21" t="n">
-        <v>13.44412896639136</v>
+        <v>13.2929729946517</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594786547202814</v>
+        <v>0.7599423901929078</v>
       </c>
       <c r="G21" t="n">
-        <v>21.91726806858818</v>
+        <v>21.3741011324832</v>
       </c>
       <c r="H21" t="n">
-        <v>38.84338397304014</v>
+        <v>38.76019615163742</v>
       </c>
       <c r="I21" t="n">
-        <v>1.74094130748687</v>
+        <v>1.977853480584169</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746741592001758</v>
+        <v>4.749639938705674</v>
       </c>
       <c r="K21" t="n">
-        <v>17.35305826100126</v>
+        <v>17.91807369974939</v>
       </c>
       <c r="L21" t="n">
-        <v>45.29925954428013</v>
+        <v>45.45118304440633</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94200934180456</v>
+        <v>99.9341244620768</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_2_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.95167949068463</v>
+        <v>43.63804780330393</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7573780521266</v>
+        <v>95.5097412812782</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0578555796608</v>
+        <v>81.38881792475489</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91985388904213</v>
+        <v>43.14437348031047</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228815645516693</v>
+        <v>2.175543235209753</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703061415287742</v>
+        <v>4.140624684759153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429385485055644</v>
+        <v>0.7375707490596103</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96972138558069</v>
+        <v>32.72379616294671</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17517323125596</v>
+        <v>33.92825445674207</v>
       </c>
       <c r="I3" t="n">
-        <v>6.59477942535436</v>
+        <v>3.073211454415043</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643365928159778</v>
+        <v>4.609817181622564</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94214442033921</v>
+        <v>18.61118207524509</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90129195866322</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632902680446</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.27307911927484</v>
+        <v>88.37165701523421</v>
       </c>
       <c r="C4" t="n">
-        <v>42.77570212135953</v>
+        <v>42.73545563907503</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191672455426708</v>
+        <v>2.181194734553063</v>
       </c>
       <c r="E4" t="n">
-        <v>6.525888169318256</v>
+        <v>6.511062000515338</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445012748031586</v>
+        <v>0.7394867673379385</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40361632378857</v>
+        <v>33.41472781108576</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2470586409453</v>
+        <v>34.01639129754516</v>
       </c>
       <c r="I4" t="n">
-        <v>5.50720928747311</v>
+        <v>6.887002108334821</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653132967519742</v>
+        <v>4.621792295862114</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72692088072515</v>
+        <v>11.62834298476581</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31418868054438</v>
+        <v>45.40722944913351</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81681168262907</v>
+        <v>99.77102807297435</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.23210288408606</v>
+        <v>87.06171828496679</v>
       </c>
       <c r="C5" t="n">
-        <v>42.58959216696357</v>
+        <v>42.49306065382676</v>
       </c>
       <c r="D5" t="n">
-        <v>2.141306536778889</v>
+        <v>2.117992245105228</v>
       </c>
       <c r="E5" t="n">
-        <v>7.142168956920791</v>
+        <v>7.281031430594654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458243870309287</v>
+        <v>0.7411152616182123</v>
       </c>
       <c r="G5" t="n">
-        <v>32.63598162630394</v>
+        <v>32.44649973478098</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30792180342272</v>
+        <v>34.09130203443775</v>
       </c>
       <c r="I5" t="n">
-        <v>4.597497154685467</v>
+        <v>5.751807193316136</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661402418943305</v>
+        <v>4.631970385113825</v>
       </c>
       <c r="K5" t="n">
-        <v>13.76789711591398</v>
+        <v>12.93828171503321</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48953268135929</v>
+        <v>44.37735201701962</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84702196423684</v>
+        <v>99.80869438587959</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.95649974742032</v>
+        <v>85.44173309268953</v>
       </c>
       <c r="C6" t="n">
-        <v>42.02821964185294</v>
+        <v>41.76551559000459</v>
       </c>
       <c r="D6" t="n">
-        <v>2.079272485099831</v>
+        <v>2.03981178879626</v>
       </c>
       <c r="E6" t="n">
-        <v>7.57476156784656</v>
+        <v>7.812628872797394</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469472125339587</v>
+        <v>0.7425037121114448</v>
       </c>
       <c r="G6" t="n">
-        <v>31.69051112218435</v>
+        <v>31.24881727831478</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35957177656211</v>
+        <v>34.15517075712645</v>
       </c>
       <c r="I6" t="n">
-        <v>3.83701550485627</v>
+        <v>4.802152482846663</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668420078337243</v>
+        <v>4.640648200696529</v>
       </c>
       <c r="K6" t="n">
-        <v>15.04350025257969</v>
+        <v>14.55826690731048</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80057185127058</v>
+        <v>43.51644508064836</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87229174570321</v>
+        <v>99.84022757796343</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.54295805951396</v>
+        <v>83.61872503685552</v>
       </c>
       <c r="C7" t="n">
-        <v>41.21086951987727</v>
+        <v>40.68771921880349</v>
       </c>
       <c r="D7" t="n">
-        <v>2.01074888786698</v>
+        <v>1.952452492810351</v>
       </c>
       <c r="E7" t="n">
-        <v>7.858730613311114</v>
+        <v>8.14606765939558</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479013820566779</v>
+        <v>0.7436900868656694</v>
       </c>
       <c r="G7" t="n">
-        <v>30.64613245810778</v>
+        <v>29.91051994479615</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40346357460719</v>
+        <v>34.20974399582078</v>
       </c>
       <c r="I7" t="n">
-        <v>3.201597505709993</v>
+        <v>4.008187814256559</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674383637854238</v>
+        <v>4.648063042910433</v>
       </c>
       <c r="K7" t="n">
-        <v>16.45704194048604</v>
+        <v>16.38127496314447</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2255047756129</v>
+        <v>42.79761269352854</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8934162359762</v>
+        <v>99.86660687547649</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.45339156921442</v>
+        <v>81.66379337391216</v>
       </c>
       <c r="C8" t="n">
-        <v>43.53838181592918</v>
+        <v>39.35449127290443</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015038410189309</v>
+        <v>1.859586591632012</v>
       </c>
       <c r="E8" t="n">
-        <v>9.709805332370816</v>
+        <v>8.31606315893907</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749496876995201</v>
+        <v>0.7447054011979566</v>
       </c>
       <c r="G8" t="n">
-        <v>31.15692144701301</v>
+        <v>28.48786438743199</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47685634177925</v>
+        <v>34.256448455106</v>
       </c>
       <c r="I8" t="n">
-        <v>5.660917679646817</v>
+        <v>3.344716622117901</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684355481220007</v>
+        <v>4.654408757487229</v>
       </c>
       <c r="K8" t="n">
-        <v>11.54660843078557</v>
+        <v>18.33620662608786</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72671418745223</v>
+        <v>42.19796355061168</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81170443416698</v>
+        <v>99.88866144960397</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.57600685159532</v>
+        <v>79.57844351857511</v>
       </c>
       <c r="C9" t="n">
-        <v>42.54011591556684</v>
+        <v>37.78741365915816</v>
       </c>
       <c r="D9" t="n">
-        <v>1.930325083050342</v>
+        <v>1.761344582123632</v>
       </c>
       <c r="E9" t="n">
-        <v>10.08926896361152</v>
+        <v>8.341812289178229</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508606627198033</v>
+        <v>0.7455758700416243</v>
       </c>
       <c r="G9" t="n">
-        <v>29.84706726962492</v>
+        <v>26.98284974782473</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53959048511096</v>
+        <v>34.29649002191471</v>
       </c>
       <c r="I9" t="n">
-        <v>4.726015245478997</v>
+        <v>2.790521819732036</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692879141998771</v>
+        <v>4.659849187760152</v>
       </c>
       <c r="K9" t="n">
-        <v>13.42399314840468</v>
+        <v>20.42155648142488</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87864322270494</v>
+        <v>41.69812106435815</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84275228667646</v>
+        <v>99.9070912049412</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.45178740133619</v>
+        <v>85.01602657654786</v>
       </c>
       <c r="C10" t="n">
-        <v>41.149693535064</v>
+        <v>41.53407224372744</v>
       </c>
       <c r="D10" t="n">
-        <v>1.835237597074658</v>
+        <v>1.763290837473045</v>
       </c>
       <c r="E10" t="n">
-        <v>10.24968622518218</v>
+        <v>10.43917342202345</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520296741280165</v>
+        <v>0.7463997185038667</v>
       </c>
       <c r="G10" t="n">
-        <v>28.37680580157678</v>
+        <v>28.63110269837113</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59336500988876</v>
+        <v>35.95282441867646</v>
       </c>
       <c r="I10" t="n">
-        <v>3.944477630185699</v>
+        <v>2.818237240850728</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700185463300103</v>
+        <v>4.664998240649166</v>
       </c>
       <c r="K10" t="n">
-        <v>15.54821259866379</v>
+        <v>14.98397342345215</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1708156650089</v>
+        <v>43.38811678033387</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8687217987367</v>
+        <v>99.90616244751347</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.19731468294445</v>
+        <v>84.54573015630547</v>
       </c>
       <c r="C11" t="n">
-        <v>39.50713069487344</v>
+        <v>41.37374632792594</v>
       </c>
       <c r="D11" t="n">
-        <v>1.735293788753534</v>
+        <v>1.733783943901082</v>
       </c>
       <c r="E11" t="n">
-        <v>10.24008172444141</v>
+        <v>10.72404554131442</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530334659295552</v>
+        <v>0.7471117717302348</v>
       </c>
       <c r="G11" t="n">
-        <v>26.83145491931543</v>
+        <v>28.20827495397907</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63953943275955</v>
+        <v>36.04340770978433</v>
       </c>
       <c r="I11" t="n">
-        <v>3.291452189685252</v>
+        <v>2.419657662282348</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706459162059721</v>
+        <v>4.669448573313967</v>
       </c>
       <c r="K11" t="n">
-        <v>17.80268531705556</v>
+        <v>15.45426984369455</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58061516501028</v>
+        <v>43.09140544344252</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89043117693927</v>
+        <v>99.919421615063</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.66203762872799</v>
+        <v>82.43307781910563</v>
       </c>
       <c r="C12" t="n">
-        <v>37.48173298167976</v>
+        <v>39.63662743793085</v>
       </c>
       <c r="D12" t="n">
-        <v>1.623789491916224</v>
+        <v>1.645053124615292</v>
       </c>
       <c r="E12" t="n">
-        <v>10.03975901614292</v>
+        <v>10.51155293560048</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538987259727841</v>
+        <v>0.7477214345912852</v>
       </c>
       <c r="G12" t="n">
-        <v>25.10735348283804</v>
+        <v>26.76464447388957</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67934139474807</v>
+        <v>36.07282007872006</v>
       </c>
       <c r="I12" t="n">
-        <v>2.746028479780045</v>
+        <v>2.018026805493419</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711867037329901</v>
+        <v>4.673258966195532</v>
       </c>
       <c r="K12" t="n">
-        <v>20.33796237127201</v>
+        <v>17.56692218089438</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08887541955698</v>
+        <v>42.72923766833359</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90857077250875</v>
+        <v>99.93278728715882</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.18671024649439</v>
+        <v>83.70506941463594</v>
       </c>
       <c r="C13" t="n">
-        <v>35.43086617905027</v>
+        <v>40.68645818347097</v>
       </c>
       <c r="D13" t="n">
-        <v>1.515978088022411</v>
+        <v>1.646270294420363</v>
       </c>
       <c r="E13" t="n">
-        <v>9.754939953798837</v>
+        <v>11.18328274240293</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546444916837086</v>
+        <v>0.7482746714072707</v>
       </c>
       <c r="G13" t="n">
-        <v>23.44035228562704</v>
+        <v>27.13873426194201</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7136466174506</v>
+        <v>36.45379695760072</v>
       </c>
       <c r="I13" t="n">
-        <v>2.290620736888614</v>
+        <v>1.857993790567207</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716528073023179</v>
+        <v>4.676716696295442</v>
       </c>
       <c r="K13" t="n">
-        <v>22.81328975350561</v>
+        <v>16.29493058536405</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67956549856135</v>
+        <v>42.95672389506457</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92372143111723</v>
+        <v>99.9381126638996</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.91299376091838</v>
+        <v>81.63919735554349</v>
       </c>
       <c r="C14" t="n">
-        <v>39.4584459158497</v>
+        <v>38.90874460421443</v>
       </c>
       <c r="D14" t="n">
-        <v>1.517900030556369</v>
+        <v>1.562165812037104</v>
       </c>
       <c r="E14" t="n">
-        <v>12.03206379733752</v>
+        <v>10.87017031270362</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556012227592058</v>
+        <v>0.7487480174129327</v>
       </c>
       <c r="G14" t="n">
-        <v>25.20290590588072</v>
+        <v>25.75227348124675</v>
       </c>
       <c r="H14" t="n">
-        <v>36.49049241253539</v>
+        <v>36.47685701808445</v>
       </c>
       <c r="I14" t="n">
-        <v>3.191522749604146</v>
+        <v>1.549307605227795</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722507642245036</v>
+        <v>4.679675108830829</v>
       </c>
       <c r="K14" t="n">
-        <v>16.08700623908162</v>
+        <v>18.36080264445653</v>
       </c>
       <c r="L14" t="n">
-        <v>44.34829845537618</v>
+        <v>42.67884181270217</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89375061030749</v>
+        <v>99.94838906137312</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.08712795715189</v>
+        <v>80.74547315045945</v>
       </c>
       <c r="C15" t="n">
-        <v>39.12431449496604</v>
+        <v>38.22433858162909</v>
       </c>
       <c r="D15" t="n">
-        <v>1.486955461424852</v>
+        <v>1.524986220252305</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23207280706835</v>
+        <v>10.83167716524727</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564083053609625</v>
+        <v>0.7491564296796916</v>
       </c>
       <c r="G15" t="n">
-        <v>24.69066789257226</v>
+        <v>25.13936862301362</v>
       </c>
       <c r="H15" t="n">
-        <v>36.53102848190528</v>
+        <v>36.49675369295041</v>
       </c>
       <c r="I15" t="n">
-        <v>2.662443100314163</v>
+        <v>1.321303333818063</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727551908506015</v>
+        <v>4.682227685498073</v>
       </c>
       <c r="K15" t="n">
-        <v>16.91287204284812</v>
+        <v>19.25452684954057</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87416005247461</v>
+        <v>42.47711513522019</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91134659028877</v>
+        <v>99.95598056638984</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.52570892686379</v>
+        <v>78.26814081104007</v>
       </c>
       <c r="C16" t="n">
-        <v>36.97446920007085</v>
+        <v>35.95137045069271</v>
       </c>
       <c r="D16" t="n">
-        <v>1.389070943139929</v>
+        <v>1.424899809975169</v>
       </c>
       <c r="E16" t="n">
-        <v>11.79697362471047</v>
+        <v>10.30438352861226</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571036476068864</v>
+        <v>0.7495079020808075</v>
       </c>
       <c r="G16" t="n">
-        <v>23.06531044542885</v>
+        <v>23.48944606719222</v>
       </c>
       <c r="H16" t="n">
-        <v>36.56461030168501</v>
+        <v>36.51387642078829</v>
       </c>
       <c r="I16" t="n">
-        <v>2.220742166749605</v>
+        <v>1.10160269438629</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73189779754304</v>
+        <v>4.684424388005047</v>
       </c>
       <c r="K16" t="n">
-        <v>19.47429107313622</v>
+        <v>21.73185918895993</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47728297400644</v>
+        <v>42.28006748996354</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9260432472135</v>
+        <v>99.96329712961617</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.22114794218984</v>
+        <v>83.43857400031817</v>
       </c>
       <c r="C17" t="n">
-        <v>38.19069579919182</v>
+        <v>39.38870784464753</v>
       </c>
       <c r="D17" t="n">
-        <v>1.390342337124854</v>
+        <v>1.425584024594702</v>
       </c>
       <c r="E17" t="n">
-        <v>12.58757000281672</v>
+        <v>12.12055277719338</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577966122306776</v>
+        <v>0.7498678040616132</v>
       </c>
       <c r="G17" t="n">
-        <v>23.48994216817073</v>
+        <v>25.11161708071372</v>
       </c>
       <c r="H17" t="n">
-        <v>37.0015977134741</v>
+        <v>38.14230156221172</v>
       </c>
       <c r="I17" t="n">
-        <v>2.257670281931023</v>
+        <v>1.201976976157934</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736228826441735</v>
+        <v>4.686673775385082</v>
       </c>
       <c r="K17" t="n">
-        <v>17.77885205781015</v>
+        <v>16.56142599968185</v>
       </c>
       <c r="L17" t="n">
-        <v>43.95526528423954</v>
+        <v>44.00981948625014</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92481314124151</v>
+        <v>99.95995333057952</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.76446175699081</v>
+        <v>85.11449587128378</v>
       </c>
       <c r="C18" t="n">
-        <v>36.0825302520788</v>
+        <v>40.13582877753916</v>
       </c>
       <c r="D18" t="n">
-        <v>1.300202853144793</v>
+        <v>1.42674643037419</v>
       </c>
       <c r="E18" t="n">
-        <v>12.08529737959498</v>
+        <v>12.73197205086741</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583928820460359</v>
+        <v>0.7504792381505586</v>
       </c>
       <c r="G18" t="n">
-        <v>21.96702855961373</v>
+        <v>25.25935737839937</v>
       </c>
       <c r="H18" t="n">
-        <v>37.03071230105669</v>
+        <v>38.17340238195575</v>
       </c>
       <c r="I18" t="n">
-        <v>1.882872268746862</v>
+        <v>2.082043153095523</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739955512787724</v>
+        <v>4.690495238440991</v>
       </c>
       <c r="K18" t="n">
-        <v>20.2355382430092</v>
+        <v>14.8855041287162</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61921844152502</v>
+        <v>44.90932219838503</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93728693661302</v>
+        <v>99.93065510464041</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.72102102700914</v>
+        <v>82.26373615760006</v>
       </c>
       <c r="C19" t="n">
-        <v>35.32899098174381</v>
+        <v>37.60696804425996</v>
       </c>
       <c r="D19" t="n">
-        <v>1.262665878537715</v>
+        <v>1.324493688402983</v>
       </c>
       <c r="E19" t="n">
-        <v>11.99807764455763</v>
+        <v>12.10886712301793</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588970909701506</v>
+        <v>0.7510072247631827</v>
       </c>
       <c r="G19" t="n">
-        <v>21.33283844747793</v>
+        <v>23.44905773623059</v>
       </c>
       <c r="H19" t="n">
-        <v>37.05533175101532</v>
+        <v>38.20025861513503</v>
       </c>
       <c r="I19" t="n">
-        <v>1.570103395886944</v>
+        <v>1.736256615280459</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743106818563441</v>
+        <v>4.693795154769892</v>
       </c>
       <c r="K19" t="n">
-        <v>21.27897897299088</v>
+        <v>17.73626384239992</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33972803780013</v>
+        <v>44.59893358130967</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94769799253481</v>
+        <v>99.94216546796956</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.0620849972582</v>
+        <v>79.24752250331964</v>
       </c>
       <c r="C20" t="n">
-        <v>32.9116129478879</v>
+        <v>34.85835887025655</v>
       </c>
       <c r="D20" t="n">
-        <v>1.166283449631338</v>
+        <v>1.216918296951813</v>
       </c>
       <c r="E20" t="n">
-        <v>11.30042954740128</v>
+        <v>11.36667840787353</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593324920581895</v>
+        <v>0.7514645595343968</v>
       </c>
       <c r="G20" t="n">
-        <v>19.70444979772965</v>
+        <v>21.54452501763556</v>
       </c>
       <c r="H20" t="n">
-        <v>37.07659146060442</v>
+        <v>38.223521116424</v>
       </c>
       <c r="I20" t="n">
-        <v>1.309170174469625</v>
+        <v>1.447761607810363</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745828075363685</v>
+        <v>4.696653497089979</v>
       </c>
       <c r="K20" t="n">
-        <v>23.93791500274181</v>
+        <v>20.75247749668035</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10685806615122</v>
+        <v>44.34093428263864</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95638601678093</v>
+        <v>99.95177064957555</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.08192630025063</v>
+        <v>76.26864471423174</v>
       </c>
       <c r="C21" t="n">
-        <v>36.56486771792108</v>
+        <v>32.10178649399214</v>
       </c>
       <c r="D21" t="n">
-        <v>1.167220211995549</v>
+        <v>1.11128538467279</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2929729946517</v>
+        <v>10.58119366854184</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599423901929078</v>
+        <v>0.7518610074037116</v>
       </c>
       <c r="G21" t="n">
-        <v>21.3741011324832</v>
+        <v>19.67438227511812</v>
       </c>
       <c r="H21" t="n">
-        <v>38.76019615163742</v>
+        <v>38.24368658306118</v>
       </c>
       <c r="I21" t="n">
-        <v>1.977853480584169</v>
+        <v>1.207104499160895</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749639938705674</v>
+        <v>4.699131296273197</v>
       </c>
       <c r="K21" t="n">
-        <v>17.91807369974939</v>
+        <v>23.73135528576828</v>
       </c>
       <c r="L21" t="n">
-        <v>45.45118304440633</v>
+        <v>44.12664262002261</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9341244620768</v>
+        <v>99.95978439978302</v>
       </c>
     </row>
   </sheetData>
